--- a/fix-errors/ig/StructureDefinition-fr-lm-dosageInstructions.xlsx
+++ b/fix-errors/ig/StructureDefinition-fr-lm-dosageInstructions.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:13:43+00:00</t>
+    <t>2026-08-18T11:25:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
